--- a/b_templates/大同要素表模版.xlsx
+++ b/b_templates/大同要素表模版.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$AR$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$AR$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>订单编号</t>
   </si>
@@ -162,60 +162,6 @@
   </si>
   <si>
     <t>履约保证金</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>申请人</t>
-  </si>
-  <si>
-    <t>被申请人</t>
-  </si>
-  <si>
-    <t>性别</t>
-  </si>
-  <si>
-    <t>民族</t>
-  </si>
-  <si>
-    <t>生日</t>
-  </si>
-  <si>
-    <t>被申请人户籍地</t>
-  </si>
-  <si>
-    <t>被申请人身份证</t>
-  </si>
-  <si>
-    <t>请求事项</t>
-  </si>
-  <si>
-    <t>事实与理由</t>
-  </si>
-  <si>
-    <t>合同签订日</t>
-  </si>
-  <si>
-    <t>设备型号</t>
-  </si>
-  <si>
-    <t>每月租金</t>
-  </si>
-  <si>
-    <t>每月还款</t>
-  </si>
-  <si>
-    <t>签约总价</t>
-  </si>
-  <si>
-    <t>已付租金+履约保证金</t>
-  </si>
-  <si>
-    <t>买断金额</t>
-  </si>
-  <si>
-    <t>买断金额的大写</t>
   </si>
 </sst>
 </file>
@@ -229,7 +175,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,14 +204,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -410,7 +348,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -426,12 +364,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -763,52 +695,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -823,77 +758,74 @@
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -923,12 +855,6 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1460,8 +1386,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AR2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:AR1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="28.125" style="1" customWidth="1"/>
@@ -1632,70 +1558,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" ht="56.25" spans="1:44">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AM2" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:AR2" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:AR1" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
